--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +781,18 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27  Jue</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>05, 16, 20, 27, 29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,18 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28  Vie</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>08, 09, 18, 21, 28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -16,7 +16,8 @@
     <sheet name="2022" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="2023" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="2024" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2025" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2026" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4749,13 +4750,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Loto Pool — 2026</t>
+          <t>Loto Pool — 2025</t>
         </is>
       </c>
     </row>
@@ -4774,360 +4775,7017 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28  Mar</t>
+          <t>2025-01-02  Jue</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01, 05, 13, 18, 20</t>
+          <t>04, 13, 20, 22, 27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29  Mié</t>
+          <t>2025-01-03  Vie</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>12, 20, 21, 25, 30</t>
+          <t>05, 07, 20, 22, 24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30  Jue</t>
+          <t>2025-01-04  Sáb</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>07, 11, 12, 20, 25</t>
+          <t>01, 03, 08, 10, 18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31  Vie</t>
+          <t>2025-01-05  Dom</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>03, 07, 12, 15, 21</t>
+          <t>13, 14, 20, 23, 24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01  Sáb</t>
+          <t>2025-01-06  Lun</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09, 11, 19, 20, 22</t>
+          <t>05, 12, 14, 21, 27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02  Dom</t>
+          <t>2025-01-07  Mar</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>02, 21, 22, 24, 29</t>
+          <t>01, 02, 12, 26, 31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03  Lun</t>
+          <t>2025-01-08  Mié</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>07, 13, 24, 25, 27</t>
+          <t>02, 06, 24, 29, 30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04  Mar</t>
+          <t>2025-01-09  Jue</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>06, 14, 15, 18, 25</t>
+          <t>02, 04, 10, 11, 25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05  Mié</t>
+          <t>2025-01-10  Vie</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>05, 06, 10, 12, 16</t>
+          <t>01, 02, 12, 22, 30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06  Jue</t>
+          <t>2025-01-11  Sáb</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>10, 13, 16, 22, 25</t>
+          <t>02, 05, 08, 27, 28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07  Vie</t>
+          <t>2025-01-12  Dom</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02, 06, 07, 14, 21</t>
+          <t>01, 05, 10, 29, 30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08  Sáb</t>
+          <t>2025-01-13  Lun</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01, 10, 13, 21, 27</t>
+          <t>01, 12, 17, 25, 27</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09  Dom</t>
+          <t>2025-01-14  Mar</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05, 14, 15, 18, 21</t>
+          <t>09, 13, 17, 29, 30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10  Lun</t>
+          <t>2025-01-15  Mié</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07, 20, 25, 27, 29</t>
+          <t>09, 22, 23, 28, 31</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11  Mar</t>
+          <t>2025-01-16  Jue</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>05, 06, 14, 27, 31</t>
+          <t>12, 13, 14, 25, 26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12  Mié</t>
+          <t>2025-01-17  Vie</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06, 09, 11, 28, 29</t>
+          <t>05, 08, 12, 13, 23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13  Jue</t>
+          <t>2025-01-18  Sáb</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>05, 08, 09, 18, 31</t>
+          <t>09, 20, 23, 28, 30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14  Vie</t>
+          <t>2025-01-19  Dom</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11, 15, 22, 23, 24</t>
+          <t>01, 10, 12, 18, 19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15  Sáb</t>
+          <t>2025-01-20  Lun</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05, 14, 19, 20, 26</t>
+          <t>05, 20, 21, 27, 30</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16  Dom</t>
+          <t>2025-01-21  Mar</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>06, 12, 20, 26, 27</t>
+          <t>18, 22, 24, 25, 31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17  Lun</t>
+          <t>2025-01-22  Mié</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>06, 13, 14, 22, 26</t>
+          <t>04, 07, 10, 26, 29</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18  Mar</t>
+          <t>2025-01-23  Jue</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>02, 05, 06, 17, 25</t>
+          <t>12, 14, 20, 24, 28</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19  Mié</t>
+          <t>2025-01-24  Vie</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03, 08, 14, 18, 24</t>
+          <t>05, 09, 17, 19, 29</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20  Jue</t>
+          <t>2025-01-25  Sáb</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>17, 23, 25, 28, 30</t>
+          <t>05, 10, 18, 20, 29</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21  Vie</t>
+          <t>2025-01-26  Dom</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06, 08, 20, 22, 28</t>
+          <t>01, 03, 14, 20, 31</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22  Sáb</t>
+          <t>2025-01-27  Lun</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>09, 15, 22, 29, 31</t>
+          <t>05, 06, 14, 28, 29</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23  Dom</t>
+          <t>2025-01-28  Mar</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>02, 12, 14, 25, 27</t>
+          <t>06, 16, 19, 25, 29</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24  Lun</t>
+          <t>2025-01-29  Mié</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>08, 09, 11, 16, 19</t>
+          <t>07, 11, 14, 17, 19</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27  Jue</t>
+          <t>2025-01-30  Jue</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>05, 16, 20, 27, 29</t>
+          <t>05, 06, 16, 27, 31</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>2025-01-31  Vie</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>01, 06, 22, 24, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01  Sáb</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>02, 07, 10, 26, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-02  Dom</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>03, 19, 23, 27, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-03  Lun</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>03, 14, 15, 20, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-04  Mar</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>02, 05, 08, 19, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-05  Mié</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>01, 07, 11, 26, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-06  Jue</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>06, 13, 16, 21, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-07  Vie</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>10, 15, 20, 27, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-08  Sáb</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>01, 04, 08, 14, 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-09  Dom</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>03, 06, 13, 28, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-10  Lun</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>02, 05, 12, 26, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-11  Mar</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>07, 09, 21, 29, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-12  Mié</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>08, 09, 20, 22, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-13  Jue</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>02, 11, 14, 21, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-14  Vie</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>06, 14, 21, 29, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-15  Sáb</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>01, 06, 09, 12, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-16  Dom</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>07, 11, 12, 22, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-17  Lun</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>12, 13, 14, 23, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-18  Mar</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>06, 11, 16, 17, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-19  Mié</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>08, 09, 16, 18, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-20  Jue</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>01, 03, 09, 11, 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-21  Vie</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>05, 09, 26, 27, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-22  Sáb</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>05, 13, 17, 21, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-23  Dom</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>09, 10, 16, 22, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-24  Lun</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>01, 02, 09, 20, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-25  Mar</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>03, 05, 14, 16, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-26  Mié</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>05, 06, 14, 24, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-27  Jue</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>02, 08, 19, 23, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-28  Vie</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>03, 10, 21, 23, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01  Sáb</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>02, 09, 11, 13, 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-02  Dom</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>01, 07, 09, 16, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-03  Lun</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>04, 07, 13, 28, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-04  Mar</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>03, 18, 19, 21, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-05  Mié</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>03, 11, 18, 29, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-06  Jue</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>02, 14, 15, 18, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-07  Vie</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>05, 06, 09, 21, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-08  Sáb</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>01, 02, 05, 11, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-09  Dom</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>09, 20, 22, 23, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-10  Lun</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>01, 09, 11, 21, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-11  Mar</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>05, 08, 09, 15, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-12  Mié</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>02, 08, 11, 12, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-13  Jue</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>06, 07, 09, 28, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-14  Vie</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>01, 04, 09, 19, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-15  Sáb</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>06, 12, 18, 25, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-16  Dom</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>05, 08, 18, 21, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-17  Lun</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>08, 14, 15, 16, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-18  Mar</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>16, 17, 20, 22, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-19  Mié</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>09, 19, 29, 30, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-20  Jue</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>06, 08, 25, 26, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-21  Vie</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>15, 19, 22, 28, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-22  Sáb</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>10, 15, 19, 28, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-23  Dom</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>04, 07, 08, 25, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-24  Lun</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>03, 15, 18, 21, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-25  Mar</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>07, 24, 25, 29, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-26  Mié</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>10, 14, 19, 25, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-27  Jue</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>04, 08, 14, 16, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-28  Vie</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 15, 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-29  Sáb</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>15, 17, 20, 21, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-30  Dom</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>04, 14, 15, 18, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-31  Lun</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>01, 14, 22, 25, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-01  Mar</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>03, 13, 20, 21, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-02  Mié</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>10, 12, 21, 24, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-03  Jue</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>03, 04, 16, 21, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-04  Vie</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>09, 10, 16, 21, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-05  Sáb</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>09, 12, 13, 22, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-06  Dom</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>08, 10, 16, 19, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-07  Lun</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>01, 03, 05, 15, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-08  Mar</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>12, 14, 20, 23, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-09  Mié</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>02, 05, 25, 26, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-10  Jue</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01, 04, 07, 15, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-11  Vie</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>06, 09, 15, 25, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-12  Sáb</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>07, 09, 11, 16, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-13  Dom</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>09, 14, 15, 17, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-14  Lun</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>02, 14, 19, 23, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-15  Mar</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>04, 08, 13, 29, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-16  Mié</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>02, 05, 07, 12, 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-19  Sáb</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>01, 04, 09, 16, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-20  Dom</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>01, 04, 17, 23, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-21  Lun</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>03, 08, 12, 21, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-22  Mar</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>01, 03, 14, 17, 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-23  Mié</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>11, 21, 23, 25, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-24  Jue</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>01, 05, 11, 17, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-25  Vie</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>01, 04, 10, 22, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-26  Sáb</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>08, 12, 16, 20, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-27  Dom</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>01, 07, 11, 15, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-28  Lun</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05, 06, 07, 17, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-29  Mar</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>09, 25, 27, 28, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-30  Mié</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>06, 15, 21, 25, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-01  Jue</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>02, 09, 20, 23, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-02  Vie</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>04, 06, 14, 23, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-03  Sáb</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02, 03, 11, 13, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-04  Dom</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02, 07, 10, 17, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-05  Lun</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>02, 07, 17, 20, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-06  Mar</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>02, 08, 13, 15, 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-07  Mié</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>11, 15, 21, 27, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-08  Jue</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>06, 07, 15, 21, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-09  Vie</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>08, 17, 27, 28, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-10  Sáb</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>01, 11, 16, 17, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-11  Dom</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>09, 10, 25, 26, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-12  Lun</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>06, 07, 20, 28, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-13  Mar</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>03, 13, 15, 19, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-14  Mié</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>11, 16, 18, 23, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-15  Jue</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>14, 16, 18, 27, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-16  Vie</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>01, 08, 14, 15, 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-17  Sáb</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>19, 21, 23, 24, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-18  Dom</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>01, 06, 13, 25, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-19  Lun</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>04, 12, 13, 18, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-20  Mar</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>06, 12, 19, 24, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-21  Mié</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>02, 09, 10, 15, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-22  Jue</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>02, 17, 22, 26, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-23  Vie</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>02, 03, 10, 21, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-24  Sáb</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>03, 08, 15, 26, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-25  Dom</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>05, 06, 12, 19, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-26  Lun</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>03, 13, 24, 30, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-27  Mar</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>06, 24, 26, 27, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-28  Mié</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>05, 09, 11, 14, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-29  Jue</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>03, 11, 15, 23, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-30  Vie</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>02, 03, 12, 16, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-31  Sáb</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>01, 07, 14, 16, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-01  Dom</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>04, 05, 09, 20, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02  Lun</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>01, 02, 03, 09, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-03  Mar</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>01, 10, 14, 16, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-04  Mié</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>11, 13, 14, 19, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-05  Jue</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>01, 08, 09, 19, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-06  Vie</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>02, 05, 06, 14, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-07  Sáb</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>11, 18, 20, 28, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-08  Dom</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>10, 23, 28, 30, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-09  Lun</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>08, 12, 13, 24, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-10  Mar</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>08, 19, 20, 26, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-11  Mié</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>02, 05, 09, 13, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-12  Jue</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>04, 12, 17, 24, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-13  Vie</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>02, 03, 08, 16, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-14  Sáb</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02, 07, 16, 21, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-15  Dom</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02, 07, 14, 15, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-16  Lun</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>03, 10, 16, 19, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-17  Mar</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>03, 08, 11, 21, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-18  Mié</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>13, 16, 22, 27, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-19  Jue</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>05, 13, 18, 21, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-20  Vie</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>10, 12, 15, 21, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-21  Sáb</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>13, 19, 23, 28, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-22  Dom</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>02, 07, 19, 23, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-23  Lun</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>03, 06, 12, 18, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-24  Mar</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>06, 14, 17, 25, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-25  Mié</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>02, 13, 18, 24, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-26  Jue</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>02, 05, 10, 12, 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-27  Vie</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03, 11, 13, 21, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-28  Sáb</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>08, 18, 23, 24, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-29  Dom</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>10, 22, 26, 29, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-30  Lun</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>04, 14, 16, 19, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01  Mar</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>02, 14, 24, 28, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-02  Mié</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>02, 03, 25, 27, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-03  Jue</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>16, 19, 20, 22, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-04  Vie</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>06, 14, 22, 28, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-05  Sáb</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>08, 16, 20, 28, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-06  Dom</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>18, 19, 20, 25, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-07  Lun</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>14, 16, 24, 25, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-08  Mar</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>05, 12, 13, 19, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-09  Mié</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>04, 17, 21, 23, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-10  Jue</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>01, 10, 12, 20, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-11  Vie</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>06, 24, 26, 27, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-12  Sáb</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>10, 13, 23, 26, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-13  Dom</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>01, 03, 16, 19, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-14  Lun</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>14, 16, 17, 22, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-15  Mar</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>01, 05, 11, 22, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-16  Mié</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>06, 08, 13, 14, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-17  Jue</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>01, 07, 11, 23, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-18  Vie</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>02, 16, 21, 26, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-19  Sáb</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>01, 06, 18, 19, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-20  Dom</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>07, 15, 16, 20, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-21  Lun</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>06, 13, 14, 15, 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-22  Mar</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>03, 06, 20, 22, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-23  Mié</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>02, 06, 10, 15, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-24  Jue</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>01, 09, 13, 19, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-25  Vie</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>09, 13, 16, 20, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-26  Sáb</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>01, 06, 11, 18, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-27  Dom</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>04, 14, 15, 17, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-28  Lun</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>13, 14, 20, 26, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-29  Mar</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>07, 10, 13, 17, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-30  Mié</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>04, 12, 16, 20, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-31  Jue</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>01, 06, 07, 18, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-01  Vie</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>04, 05, 06, 16, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-02  Sáb</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>05, 08, 09, 18, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-03  Dom</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>02, 04, 06, 14, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-04  Lun</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>03, 05, 06, 24, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-05  Mar</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>01, 05, 07, 13, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-06  Mié</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>02, 19, 22, 28, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-07  Jue</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>04, 05, 07, 09, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-08  Vie</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>10, 19, 22, 25, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-09  Sáb</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>06, 13, 14, 27, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-10  Dom</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>07, 11, 15, 24, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-11  Lun</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>12, 20, 21, 28, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-12  Mar</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>02, 15, 22, 25, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-13  Mié</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>06, 10, 12, 15, 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-14  Jue</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>13, 14, 17, 21, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-15  Vie</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>02, 06, 12, 21, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-16  Sáb</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>06, 07, 09, 20, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-17  Dom</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>01, 04, 06, 07, 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-18  Lun</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>01, 05, 14, 17, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-19  Mar</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>04, 07, 08, 14, 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-20  Mié</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>09, 14, 17, 22, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-21  Jue</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>01, 12, 13, 20, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-22  Vie</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>03, 05, 24, 27, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-23  Sáb</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>02, 07, 08, 13, 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-24  Dom</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>06, 11, 13, 19, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-25  Lun</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>01, 05, 13, 25, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-26  Mar</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>09, 11, 14, 21, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-27  Mié</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>01, 03, 07, 10, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28  Jue</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>05, 14, 24, 26, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-29  Vie</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>05, 13, 14, 18, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-30  Sáb</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>05, 08, 17, 27, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-31  Dom</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>01, 14, 24, 29, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-01  Lun</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>09, 11, 16, 26, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-02  Mar</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>07, 11, 12, 21, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-03  Mié</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>02, 06, 23, 26, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-04  Jue</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>05, 10, 16, 20, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-05  Vie</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>10, 12, 14, 17, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-06  Sáb</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>02, 10, 15, 19, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-07  Dom</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>04, 09, 12, 19, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-08  Lun</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>14, 17, 21, 25, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-09  Mar</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>10, 16, 23, 24, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-10  Mié</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>02, 04, 13, 18, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-11  Jue</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>01, 02, 14, 30, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-12  Vie</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>01, 15, 16, 19, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-13  Sáb</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>01, 04, 09, 26, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-14  Dom</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>04, 19, 21, 24, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-15  Lun</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>03, 06, 09, 21, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-16  Mar</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>05, 10, 11, 16, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-17  Mié</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>01, 07, 15, 18, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-18  Jue</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>01, 02, 13, 22, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-19  Vie</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>02, 03, 06, 18, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-20  Sáb</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>11, 14, 26, 29, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-21  Dom</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>01, 16, 20, 21, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-22  Lun</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>03, 05, 26, 27, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-23  Mar</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>13, 17, 20, 22, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-24  Mié</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>06, 18, 20, 25, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-25  Jue</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>10, 11, 16, 19, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-26  Vie</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>03, 04, 05, 21, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-27  Sáb</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>03, 06, 15, 16, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-28  Dom</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>12, 13, 25, 28, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-29  Lun</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>09, 21, 25, 30, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-30  Mar</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>08, 09, 13, 20, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-01  Mié</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>01, 05, 12, 26, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-02  Jue</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>03, 06, 14, 17, 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-03  Vie</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>05, 06, 15, 27, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-04  Sáb</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>05, 06, 12, 25, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-05  Dom</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>04, 05, 13, 19, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-06  Lun</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>04, 18, 20, 21, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-07  Mar</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>02, 06, 07, 27, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-08  Mié</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>05, 07, 14, 18, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-09  Jue</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>07, 08, 10, 14, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-10  Vie</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>03, 05, 06, 10, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-11  Sáb</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>05, 06, 15, 21, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-12  Dom</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>18, 21, 22, 24, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-13  Lun</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>03, 09, 12, 28, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-14  Mar</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>14, 17, 18, 21, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-15  Mié</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>07, 13, 20, 22, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-16  Jue</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>11, 19, 23, 26, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-17  Vie</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>05, 13, 20, 24, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-18  Sáb</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>05, 08, 23, 28, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-19  Dom</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>05, 11, 12, 28, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-20  Lun</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>09, 10, 13, 15, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-21  Mar</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>04, 08, 18, 19, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-26  Dom</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>14, 16, 23, 25, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-27  Lun</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>01, 11, 19, 21, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-28  Mar</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>06, 08, 15, 23, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-29  Mié</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>04, 07, 10, 23, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-30  Jue</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>07, 20, 21, 26, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-31  Vie</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>07, 08, 11, 14, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-01  Sáb</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>03, 05, 06, 21, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-02  Dom</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>02, 04, 10, 24, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-03  Lun</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>03, 15, 22, 23, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-04  Mar</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>02, 03, 08, 10, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-05  Mié</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>16, 18, 19, 21, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-06  Jue</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>07, 10, 28, 29, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-07  Vie</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>17, 20, 23, 25, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-08  Sáb</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>03, 04, 06, 10, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-09  Dom</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>01, 10, 14, 17, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-10  Lun</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>03, 07, 15, 16, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-11  Mar</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>01, 06, 11, 17, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-12  Mié</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>18, 19, 26, 30, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-13  Jue</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>02, 03, 09, 11, 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-14  Vie</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>02, 06, 17, 22, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-15  Sáb</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>02, 06, 08, 18, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-16  Dom</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>07, 15, 28, 29, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-17  Lun</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>08, 13, 17, 27, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-18  Mar</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>01, 21, 22, 24, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-19  Mié</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>02, 03, 04, 16, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-20  Jue</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>04, 06, 17, 21, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-21  Vie</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>01, 03, 19, 22, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-22  Sáb</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>15, 16, 22, 28, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-23  Dom</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>03, 05, 09, 15, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-24  Lun</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>02, 07, 08, 09, 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-25  Mar</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>03, 11, 15, 17, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-26  Mié</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>02, 03, 09, 10, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-27  Jue</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>08, 17, 20, 23, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-28  Vie</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>01, 09, 10, 12, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-29  Sáb</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>03, 11, 17, 18, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-30  Dom</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>05, 09, 13, 21, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-01  Lun</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>02, 15, 20, 30, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-02  Mar</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>03, 07, 20, 25, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-03  Mié</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>11, 15, 24, 25, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-04  Jue</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>03, 13, 17, 29, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-05  Vie</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>07, 11, 13, 27, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-06  Sáb</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>02, 03, 08, 10, 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-07  Dom</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>01, 03, 05, 12, 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-08  Lun</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>03, 06, 09, 13, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-09  Mar</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>08, 09, 10, 14, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-10  Mié</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>05, 12, 14, 18, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-11  Jue</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>06, 07, 15, 18, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-12  Vie</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>05, 17, 18, 30, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-13  Sáb</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>10, 17, 20, 22, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-14  Dom</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>05, 12, 19, 26, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-15  Lun</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>01, 03, 08, 10, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-16  Mar</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>04, 17, 20, 21, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-17  Mié</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>15, 22, 23, 28, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-18  Jue</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>02, 03, 08, 21, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-19  Vie</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>15, 16, 21, 22, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-20  Sáb</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>06, 07, 25, 27, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-21  Dom</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>03, 06, 15, 18, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-22  Lun</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>10, 12, 13, 19, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-23  Mar</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>04, 07, 08, 09, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-26  Vie</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>01, 02, 09, 19, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-27  Sáb</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>01, 04, 08, 18, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-28  Dom</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>06, 14, 16, 18, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-29  Lun</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>03, 10, 12, 22, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-30  Mar</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>10, 12, 16, 27, 30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B229"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Loto Pool — 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>NÚMEROS GANADORES (5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28  Mar</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>01, 05, 13, 18, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29  Mié</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>12, 20, 21, 25, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30  Jue</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>07, 11, 12, 20, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31  Vie</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>03, 07, 12, 15, 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01  Sáb</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>09, 11, 19, 20, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02  Dom</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>02, 21, 22, 24, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03  Lun</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>07, 13, 24, 25, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04  Mar</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>06, 14, 15, 18, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05  Mié</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>05, 06, 10, 12, 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06  Jue</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>10, 13, 16, 22, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07  Vie</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>02, 06, 07, 14, 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08  Sáb</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>01, 10, 13, 21, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09  Dom</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>05, 14, 15, 18, 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10  Lun</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>07, 20, 25, 27, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11  Mar</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>05, 06, 14, 27, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12  Mié</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>06, 09, 11, 28, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13  Jue</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>05, 08, 09, 18, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14  Vie</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>11, 15, 22, 23, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15  Sáb</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>05, 14, 19, 20, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16  Dom</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>06, 12, 20, 26, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17  Lun</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>06, 13, 14, 22, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18  Mar</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>02, 05, 06, 17, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19  Mié</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>03, 08, 14, 18, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20  Jue</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>17, 23, 25, 28, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21  Vie</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>06, 08, 20, 22, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22  Sáb</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>09, 15, 22, 29, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23  Dom</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>02, 12, 14, 25, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24  Lun</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>08, 09, 11, 16, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27  Jue</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>05, 16, 20, 27, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28  Vie</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>08, 09, 18, 21, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-02  Vie</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>07, 08, 27, 28, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-03  Sáb</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>16, 19, 20, 26, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-04  Dom</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>02, 07, 08, 29, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-05  Lun</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>07, 10, 14, 22, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-06  Mar</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>11, 14, 22, 23, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-07  Mié</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>08, 09, 14, 16, 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-08  Jue</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>02, 07, 10, 26, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-09  Vie</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>03, 15, 23, 28, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-10  Sáb</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>01, 09, 16, 20, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-11  Dom</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>09, 15, 17, 19, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-12  Lun</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>10, 21, 22, 23, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-13  Mar</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>04, 11, 19, 22, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-14  Mié</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>04, 09, 11, 23, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-15  Jue</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>12, 13, 15, 19, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-16  Vie</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>07, 13, 14, 18, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-17  Sáb</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>01, 04, 18, 20, 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-18  Dom</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>02, 05, 07, 25, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-19  Lun</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>08, 17, 18, 29, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-20  Mar</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>06, 15, 20, 24, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-21  Mié</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>02, 17, 18, 27, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-22  Jue</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>04, 08, 25, 27, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-23  Vie</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>04, 16, 26, 28, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-24  Sáb</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>05, 11, 15, 22, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-25  Dom</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>01, 11, 13, 23, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-26  Lun</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>13, 14, 17, 18, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-27  Mar</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>07, 11, 13, 18, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-28  Mié</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>07, 15, 17, 21, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-29  Jue</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>03, 06, 17, 23, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-30  Vie</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>11, 14, 20, 23, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31  Sáb</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>04, 10, 15, 24, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-01  Dom</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>01, 03, 05, 15, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-02  Lun</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>03, 11, 19, 20, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-03  Mar</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>02, 20, 23, 24, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-04  Mié</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>08, 12, 13, 19, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-05  Jue</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>02, 05, 12, 19, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-06  Vie</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>04, 14, 17, 21, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-07  Sáb</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>01, 03, 04, 07, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-08  Dom</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>01, 15, 17, 21, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09  Lun</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>02, 05, 07, 08, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-10  Mar</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>01, 08, 10, 11, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-11  Mié</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>06, 09, 14, 26, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-12  Jue</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>11, 12, 18, 23, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13  Vie</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>06, 08, 19, 22, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-14  Sáb</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>01, 05, 08, 13, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-15  Dom</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03, 04, 19, 25, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16  Lun</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02, 06, 15, 18, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17  Mar</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>01, 08, 14, 19, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-18  Mié</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>02, 11, 13, 22, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-19  Jue</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>04, 09, 11, 25, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-20  Vie</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>05, 15, 20, 24, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-21  Sáb</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>07, 10, 14, 23, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-22  Dom</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>02, 04, 19, 25, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-23  Lun</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>04, 13, 19, 21, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-24  Mar</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>06, 11, 24, 27, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-25  Mié</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>10, 15, 19, 21, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-26  Jue</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>06, 09, 17, 20, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-27  Vie</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01, 23, 25, 26, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28  Sáb</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>14, 15, 18, 25, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01  Dom</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>04, 06, 08, 10, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-02  Lun</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>01, 02, 09, 11, 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-03  Mar</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>04, 05, 07, 10, 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-04  Mié</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>08, 15, 21, 23, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-05  Jue</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>08, 20, 21, 22, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-06  Vie</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>14, 15, 16, 21, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-07  Sáb</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>05, 10, 15, 20, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-08  Dom</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>03, 08, 11, 15, 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-09  Lun</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>09, 13, 26, 28, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-10  Mar</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>10, 19, 21, 22, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-11  Mié</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>04, 05, 11, 23, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-12  Jue</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>07, 08, 22, 24, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13  Vie</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>06, 19, 23, 26, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-14  Sáb</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>08, 10, 12, 18, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-15  Dom</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>16, 21, 24, 28, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16  Lun</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10, 14, 15, 17, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17  Mar</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>02, 03, 05, 14, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18  Mié</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>02, 03, 07, 09, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19  Jue</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>10, 14, 21, 27, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20  Vie</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>12, 17, 21, 22, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21  Sáb</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>03, 05, 09, 14, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-22  Dom</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>08, 10, 14, 16, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-23  Lun</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>01, 04, 09, 10, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24  Mar</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>04, 10, 12, 14, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-25  Mié</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>01, 17, 23, 24, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-26  Jue</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>10, 11, 15, 26, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27  Vie</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>03, 04, 06, 11, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-28  Sáb</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>10, 11, 19, 22, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29  Dom</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>06, 09, 10, 15, 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30  Lun</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03, 07, 09, 19, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31  Mar</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>14, 15, 29, 30, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01  Mié</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>01, 03, 16, 17, 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04  Sáb</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>06, 17, 18, 20, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-05  Dom</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>06, 16, 23, 24, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06  Lun</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>05, 09, 15, 23, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07  Mar</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>02, 15, 21, 23, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08  Mié</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>05, 06, 16, 30, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-09  Jue</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>04, 13, 21, 25, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10  Vie</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>02, 06, 10, 17, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11  Sáb</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>06, 14, 28, 30, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-12  Dom</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>09, 20, 23, 30, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13  Lun</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>03, 11, 16, 18, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14  Mar</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>02, 12, 17, 23, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15  Mié</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>06, 11, 12, 18, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16  Jue</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>11, 18, 20, 27, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17  Vie</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>09, 11, 13, 15, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18  Sáb</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>02, 04, 06, 07, 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19  Dom</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>07, 09, 13, 24, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20  Lun</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>14, 16, 20, 26, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21  Mar</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>09, 10, 12, 18, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22  Mié</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14, 17, 19, 21, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23  Jue</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>06, 07, 09, 14, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24  Vie</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>01, 22, 23, 24, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25  Sáb</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12, 13, 16, 25, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26  Dom</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>06, 13, 17, 30, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27  Lun</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>14, 15, 17, 18, 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28  Mar</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>03, 07, 09, 20, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29  Mié</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>03, 05, 11, 17, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30  Jue</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>05, 08, 10, 12, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01  Vie</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>14, 15, 16, 26, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02  Sáb</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>04, 11, 16, 17, 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03  Dom</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>03, 10, 14, 19, 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04  Lun</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08, 11, 15, 19, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05  Mar</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>19, 21, 22, 30, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06  Mié</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>05, 23, 25, 29, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07  Jue</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>02, 05, 11, 16, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08  Vie</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>02, 07, 24, 25, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09  Sáb</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>01, 05, 24, 25, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10  Dom</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>03, 07, 08, 14, 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11  Lun</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>06, 22, 23, 24, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12  Mar</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>03, 12, 13, 23, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13  Mié</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>02, 06, 08, 22, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14  Jue</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>19, 24, 25, 28, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15  Vie</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>13, 15, 17, 21, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16  Sáb</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>13, 16, 22, 26, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17  Dom</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>03, 11, 23, 26, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18  Lun</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>02, 09, 13, 14, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19  Mar</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>15, 17, 22, 26, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20  Mié</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>01, 05, 12, 21, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21  Jue</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>06, 14, 19, 20, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22  Vie</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>01, 05, 10, 25, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-23  Sáb</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>14, 18, 23, 24, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24  Dom</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>09, 10, 13, 15, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25  Lun</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>03, 05, 19, 22, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26  Mar</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04, 05, 24, 25, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27  Mié</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>05, 06, 13, 23, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28  Jue</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>09, 19, 20, 23, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29  Vie</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>03, 14, 22, 23, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30  Sáb</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>05, 15, 21, 23, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31  Dom</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>05, 07, 19, 22, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01  Lun</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>02, 09, 17, 24, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02  Mar</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>03, 08, 09, 17, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03  Mié</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>05, 16, 18, 21, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04  Jue</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 16, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05  Vie</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>04, 06, 08, 15, 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06  Sáb</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>11, 14, 18, 24, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07  Dom</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>07, 13, 15, 19, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08  Lun</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>09, 16, 17, 24, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09  Mar</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>08, 09, 12, 16, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10  Mié</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>01, 12, 17, 20, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11  Jue</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>02, 08, 19, 21, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12  Vie</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>05, 09, 16, 17, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13  Sáb</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>04, 13, 18, 20, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14  Dom</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>03, 10, 11, 20, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15  Lun</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>06, 12, 13, 18, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16  Mar</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>03, 07, 09, 25, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17  Mié</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>07, 12, 14, 27, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18  Jue</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>05, 10, 11, 12, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19  Vie</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>04, 05, 17, 18, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20  Sáb</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>06, 09, 19, 27, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21  Dom</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>05, 06, 10, 19, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22  Lun</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>01, 04, 10, 13, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24  Mié</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>12, 18, 23, 29, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28  Dom</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>12, 14, 25, 27, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29  Lun</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>02, 19, 22, 24, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30  Mar</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>08, 17, 18, 23, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01  Mié</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>02, 04, 08, 11, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02  Jue</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>13, 14, 17, 22, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03  Vie</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>11, 20, 21, 22, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04  Sáb</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>07, 11, 15, 28, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05  Dom</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>08, 12, 21, 27, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06  Lun</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>06, 12, 14, 16, 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07  Mar</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>09, 12, 13, 19, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09  Jue</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>11, 15, 19, 27, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10  Vie</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>15, 16, 17, 26, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13  Lun</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>06, 20, 25, 28, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14  Mar</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>02, 03, 04, 05, 07</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15  Mié</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>19, 24, 26, 27, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16  Jue</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>01, 13, 15, 21, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17  Vie</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>01, 07, 10, 11, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18  Sáb</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>02, 18, 22, 24, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19  Dom</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>06, 17, 22, 25, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20  Lun</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>01, 18, 21, 23, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21  Mar</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>03, 14, 19, 20, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22  Mié</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>11, 21, 23, 29, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24  Vie</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>04, 09, 20, 23, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25  Sáb</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>08, 18, 23, 27, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26  Dom</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>03, 20, 22, 24, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27  Lun</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>02, 04, 13, 18, 30</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B229"/>
+  <dimension ref="A1:B230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11786,6 +11786,18 @@
       <c r="B229" s="2" t="inlineStr">
         <is>
           <t>02, 04, 13, 18, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29  Sáb</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>12, 24, 27, 29, 31</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B230"/>
+  <dimension ref="A1:B231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11798,6 +11798,18 @@
       <c r="B230" s="2" t="inlineStr">
         <is>
           <t>12, 24, 27, 29, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02  Mié</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>08, 21, 23, 24, 28</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B231"/>
+  <dimension ref="A1:B232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11810,6 +11810,18 @@
       <c r="B231" s="2" t="inlineStr">
         <is>
           <t>08, 21, 23, 24, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04  Vie</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>07, 08, 12, 13, 20</t>
         </is>
       </c>
     </row>
